--- a/src/main/resources/python/evaluation_dataset.xlsx
+++ b/src/main/resources/python/evaluation_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sergio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57191C03-A0E4-4492-8E54-E0E15F70E0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF667C0F-3851-457E-A3BD-F41A42CD7BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1395" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,12 +52,6 @@
     <t>Cuántas veces aparece la calefacción y en qué contexto fue tratada.</t>
   </si>
   <si>
-    <t>¿Cuándo se trató el tema de limpieza?</t>
-  </si>
-  <si>
-    <t>¿En qué reuniones hubo exactamente 21 asistentes?</t>
-  </si>
-  <si>
     <t>¿Quiénes estuvieron presentes en la reunión del 25 de febrero de 2026?</t>
   </si>
   <si>
@@ -425,6 +419,12 @@
   </si>
   <si>
     <t>No existe acta correspondiente al 25/09/2025.</t>
+  </si>
+  <si>
+    <t>¿Cuándo se trató el tema de limpieza y qé se habló sobre ello?</t>
+  </si>
+  <si>
+    <t>¿En qué reuniones hubo exactamente 21 asistentes y qué se decidió en esa reunión?</t>
   </si>
 </sst>
 </file>
@@ -471,9 +471,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -485,17 +483,61 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -506,6 +548,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{15666F62-24D3-4988-9087-5DB50AE2DCE3}" name="Tabla1" displayName="Tabla1" ref="A1:C61" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:C61" xr:uid="{15666F62-24D3-4988-9087-5DB50AE2DCE3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{873BA437-481D-4B4B-BB26-9FA9A16646E8}" name="Pregunta"/>
+    <tableColumn id="2" xr3:uid="{FDA6D0F4-8A7A-4DF8-B85A-1040C03F6C5E}" name="Respuesta"/>
+    <tableColumn id="3" xr3:uid="{DB0153DB-E877-4EBB-B6DE-180209F284CE}" name="QueryType"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -804,13 +858,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -819,21 +873,21 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +895,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +906,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +917,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +928,10 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +939,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,585 +950,588 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
         <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
         <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
         <v>57</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
         <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" t="s">
         <v>77</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s">
         <v>88</v>
-      </c>
-      <c r="B47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
         <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>110</v>
-      </c>
-      <c r="B57" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>